--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/FLORIDA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/FLORIDA_2018.xlsx
@@ -2371,7 +2371,7 @@
         <v>24</v>
       </c>
       <c r="D112">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="113">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C163">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C355">
@@ -7429,7 +7429,7 @@
         <v>25</v>
       </c>
       <c r="D393">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="394">
@@ -7987,7 +7987,7 @@
         <v>24</v>
       </c>
       <c r="D424">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="425">
@@ -8023,7 +8023,7 @@
         <v>25</v>
       </c>
       <c r="D426">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="427">
@@ -8977,7 +8977,7 @@
         <v>25</v>
       </c>
       <c r="D479">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="480">
@@ -10687,7 +10687,7 @@
         <v>24</v>
       </c>
       <c r="D574">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="575">
@@ -11731,7 +11731,7 @@
         <v>25</v>
       </c>
       <c r="D632">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="633">
@@ -12469,7 +12469,7 @@
         <v>24</v>
       </c>
       <c r="D673">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="674">
@@ -12595,7 +12595,7 @@
         <v>25</v>
       </c>
       <c r="D680">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="681">
@@ -12685,7 +12685,7 @@
         <v>24</v>
       </c>
       <c r="D685">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="686">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C783">
@@ -14755,7 +14755,7 @@
         <v>24</v>
       </c>
       <c r="D800">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="801">
@@ -15187,7 +15187,7 @@
         <v>24</v>
       </c>
       <c r="D824">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="825">
@@ -15385,7 +15385,7 @@
         <v>24</v>
       </c>
       <c r="D835">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="836">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C925">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C926">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C984">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C985">
@@ -18859,7 +18859,7 @@
         <v>25</v>
       </c>
       <c r="D1028">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="1029">
@@ -21001,7 +21001,7 @@
         <v>24</v>
       </c>
       <c r="D1147">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="1148">
@@ -23251,7 +23251,7 @@
         <v>25</v>
       </c>
       <c r="D1272">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="1273">
@@ -23971,7 +23971,7 @@
         <v>24</v>
       </c>
       <c r="D1312">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="1313">
@@ -24241,7 +24241,7 @@
         <v>24</v>
       </c>
       <c r="D1327">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="1328">
@@ -25105,7 +25105,7 @@
         <v>25</v>
       </c>
       <c r="D1375">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="1376">
@@ -25519,7 +25519,7 @@
         <v>24</v>
       </c>
       <c r="D1398">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="1399">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1456">
@@ -27643,7 +27643,7 @@
         <v>25</v>
       </c>
       <c r="D1516">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="1517">
@@ -29209,7 +29209,7 @@
         <v>25</v>
       </c>
       <c r="D1603">
-        <v>0.0009411941871846999</v>
+        <v>0.0009411941871847</v>
       </c>
     </row>
     <row r="1604">
@@ -29875,7 +29875,7 @@
         <v>24</v>
       </c>
       <c r="D1640">
-        <v>0.0009035464196973119</v>
+        <v>0.000903546419697312</v>
       </c>
     </row>
     <row r="1641">
